--- a/Reports/Members/Kelvin_Activity_Report.xlsx
+++ b/Reports/Members/Kelvin_Activity_Report.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -440,15 +440,25 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
+          <t>Steps</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
           <t>Points</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>App</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
         <is>
           <t>Image Link</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -482,10 +492,20 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
           <t>View</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
@@ -514,20 +534,25 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>Strava</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>Flagged</t>
         </is>
@@ -544,7 +569,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -560,6 +585,11 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
+          <t>Total Steps</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
           <t>Total Points</t>
         </is>
       </c>
@@ -574,6 +604,9 @@
         <v>12.66</v>
       </c>
       <c r="C2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" t="n">
         <v>2</v>
       </c>
     </row>
@@ -589,6 +622,9 @@
       <c r="C3" t="n">
         <v>0</v>
       </c>
+      <c r="D3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -602,6 +638,9 @@
       <c r="C4" t="n">
         <v>0</v>
       </c>
+      <c r="D4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -619,6 +658,11 @@
           <t>---</t>
         </is>
       </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -630,6 +674,9 @@
         <v>12.66</v>
       </c>
       <c r="C6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" t="n">
         <v>2</v>
       </c>
     </row>

--- a/Reports/Members/Kelvin_Activity_Report.xlsx
+++ b/Reports/Members/Kelvin_Activity_Report.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -440,25 +440,15 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Steps</t>
+          <t>Points</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Points</t>
+          <t>Image Link</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
-        <is>
-          <t>App</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>Image Link</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -492,20 +482,10 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>View</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
@@ -555,6 +535,100 @@
       <c r="I3" t="inlineStr">
         <is>
           <t>Flagged</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>5/20/2026 19:07:24</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kelvin</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Run/Jog</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>5.31</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Garmin</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>5/20/2026 19:19:30</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kelvin</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Steps</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>3.02</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Garmin</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Verified</t>
         </is>
       </c>
     </row>
@@ -601,13 +675,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>12.66</v>
+        <v>17.97</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -633,7 +707,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
@@ -671,13 +745,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>12.66</v>
+        <v>20.99</v>
       </c>
       <c r="C6" t="n">
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/Reports/Members/Kelvin_Activity_Report.xlsx
+++ b/Reports/Members/Kelvin_Activity_Report.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sessions" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Sessions" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -440,15 +440,25 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
+          <t>Steps</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
           <t>Points</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>App</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
         <is>
           <t>Image Link</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -457,7 +467,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-16 17:39:10</t>
+          <t>2026-05-18 18:45:40</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -472,7 +482,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>5.34</t>
+          <t>7.32</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -482,19 +492,29 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Strava</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
           <t>View</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Verified</t>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Flagged</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-18 18:45:40</t>
+          <t>5/20/2026 19:07:24</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -509,7 +529,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>7.32</t>
+          <t>5.31</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -519,12 +539,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Strava</t>
+          <t>Garmin</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -534,14 +554,14 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Flagged</t>
+          <t>Verified</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>5/20/2026 19:07:24</t>
+          <t>5/20/2026 19:19:30</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -551,12 +571,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Run/Jog</t>
+          <t>Steps</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>5.31</t>
+          <t>3.02</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -566,7 +586,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -588,7 +608,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>5/20/2026 19:19:30</t>
+          <t>5/23/2026 14:39:30</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -598,12 +618,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Steps</t>
+          <t>Run/Jog</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>5.02</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -613,20 +633,57 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Committee Approval Required</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-05-16 17:39:10</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kelvin</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Run/Jog</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>5.34</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Garmin</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>View</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
@@ -675,13 +732,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>17.97</v>
+        <v>17.65</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
@@ -745,13 +802,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>20.99</v>
+        <v>20.67</v>
       </c>
       <c r="C6" t="n">
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>

--- a/Reports/Members/Kelvin_Activity_Report.xlsx
+++ b/Reports/Members/Kelvin_Activity_Report.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sessions" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Summary" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sessions" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I6"/>
+  <dimension ref="A1:I5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -467,7 +467,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-18 18:45:40</t>
+          <t>2026-05-16 17:39:10</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -482,24 +482,16 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>7.32</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
+          <t>5.34</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Strava</t>
-        </is>
-      </c>
+      <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
           <t>View</t>
@@ -507,14 +499,14 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Flagged</t>
+          <t>Verified</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>5/20/2026 19:07:24</t>
+          <t>2026-05-18 18:45:40</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -529,7 +521,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>5.31</t>
+          <t>7.32</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -539,12 +531,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Garmin</t>
+          <t>Strava</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -554,14 +546,14 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Verified</t>
+          <t>Flagged</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>5/20/2026 19:19:30</t>
+          <t>5/20/2026 19:07:24</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -571,12 +563,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Steps</t>
+          <t>Run/Jog</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>5.31</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -586,7 +578,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -608,7 +600,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>5/23/2026 14:39:30</t>
+          <t>5/20/2026 19:19:30</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -618,12 +610,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Run/Jog</t>
+          <t>Steps</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>5.02</t>
+          <t>3.02</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -633,12 +625,12 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Garmin</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -647,43 +639,6 @@
         </is>
       </c>
       <c r="I5" t="inlineStr">
-        <is>
-          <t>Committee Approval Required</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>2026-05-16 17:39:10</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Kelvin</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Run/Jog</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>5.34</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
@@ -732,13 +687,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>17.65</v>
+        <v>17.97</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3">
@@ -802,13 +757,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>20.67</v>
+        <v>20.99</v>
       </c>
       <c r="C6" t="n">
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/Reports/Members/Kelvin_Activity_Report.xlsx
+++ b/Reports/Members/Kelvin_Activity_Report.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,12 +531,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Strava</t>
+          <t>Garmin</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -546,14 +546,14 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Flagged</t>
+          <t>Verified</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>5/20/2026 19:07:24</t>
+          <t>2026-05-20 19:07:24</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -578,7 +578,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -600,7 +600,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>5/20/2026 19:19:30</t>
+          <t>2026-05-20 19:19:30</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -641,6 +641,53 @@
       <c r="I5" t="inlineStr">
         <is>
           <t>Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-05-23 14:39:30</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kelvin</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Run/Jog</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>5.02</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Committee Approval Required</t>
         </is>
       </c>
     </row>
@@ -687,13 +734,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>17.97</v>
+        <v>22.99</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -757,13 +804,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>20.99</v>
+        <v>26.01</v>
       </c>
       <c r="C6" t="n">
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/Reports/Members/Kelvin_Activity_Report.xlsx
+++ b/Reports/Members/Kelvin_Activity_Report.xlsx
@@ -677,7 +677,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Garmin</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -687,7 +687,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Committee Approval Required</t>
+          <t>Verified</t>
         </is>
       </c>
     </row>

--- a/Reports/Members/Kelvin_Activity_Report.xlsx
+++ b/Reports/Members/Kelvin_Activity_Report.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sessions" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Sessions" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I6"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -467,7 +467,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-16 17:39:10</t>
+          <t>2026-05-18 18:45:40</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -482,16 +482,24 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>5.34</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr"/>
+          <t>7.32</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="F2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Garmin</t>
+        </is>
+      </c>
       <c r="H2" t="inlineStr">
         <is>
           <t>View</t>
@@ -506,7 +514,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-18 18:45:40</t>
+          <t>2026-05-20 19:07:24</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -521,7 +529,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>7.32</t>
+          <t>5.31</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -553,7 +561,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-20 19:07:24</t>
+          <t>2026-05-20 19:19:30</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -563,12 +571,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Run/Jog</t>
+          <t>Steps</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>5.31</t>
+          <t>3.02</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -600,7 +608,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-20 19:19:30</t>
+          <t>2026-05-23 14:39:30</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -610,12 +618,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Steps</t>
+          <t>Run/Jog</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>5.02</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -647,7 +655,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-05-23 14:39:30</t>
+          <t>2026-05-25 18:37:29</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -662,7 +670,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>5.02</t>
+          <t>7.57</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -686,6 +694,45 @@
         </is>
       </c>
       <c r="I6" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-05-16 17:39:10</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kelvin</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Run/Jog</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>5.34</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
@@ -734,7 +781,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>22.99</v>
+        <v>30.56</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
@@ -804,7 +851,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>26.01</v>
+        <v>33.58</v>
       </c>
       <c r="C6" t="n">
         <v>0</v>

--- a/Reports/Members/Kelvin_Activity_Report.xlsx
+++ b/Reports/Members/Kelvin_Activity_Report.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:I11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -467,7 +467,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-18 18:45:40</t>
+          <t>2026-05-25 18:37:29</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -482,7 +482,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>7.32</t>
+          <t>7.57</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -514,7 +514,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-20 19:07:24</t>
+          <t>2026-05-27 09:35:55</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -529,7 +529,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>5.31</t>
+          <t>7.56</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -561,7 +561,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-20 19:19:30</t>
+          <t>2026-05-29 18:09:22</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -571,12 +571,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Steps</t>
+          <t>Run/Jog</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>7.56</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -591,7 +591,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Garmin</t>
+          <t>Garmin Forerunner 265</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -608,7 +608,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-23 14:39:30</t>
+          <t>2026-05-30 10:55:11</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -623,7 +623,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>5.02</t>
+          <t>8.16</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Garmin</t>
+          <t>Southwest</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -655,7 +655,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-05-25 18:37:29</t>
+          <t>5/31/2026 18:29:41</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -665,12 +665,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Run/Jog</t>
+          <t>Steps</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>7.57</t>
+          <t>31.00</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -685,7 +685,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Garmin</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -695,14 +695,14 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Verified</t>
+          <t>Committee Approval Required</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-05-16 17:39:10</t>
+          <t>2026-05-18 18:45:40</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -717,16 +717,24 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>5.34</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr"/>
+          <t>7.32</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="F7" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Garmin</t>
+        </is>
+      </c>
       <c r="H7" t="inlineStr">
         <is>
           <t>View</t>
@@ -735,6 +743,194 @@
       <c r="I7" t="inlineStr">
         <is>
           <t>Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-05-20 19:07:24</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kelvin</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Run/Jog</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>5.31</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Garmin</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-05-20 19:19:30</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kelvin</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Steps</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>3.02</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Garmin</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-05-23 14:39:30</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kelvin</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Run/Jog</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>5.02</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Garmin</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>6/1/2026 11:41:23</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kelvin</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Run/Jog</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>10.44</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Strava</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Flagged</t>
         </is>
       </c>
     </row>
@@ -781,13 +977,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>30.56</v>
+        <v>58.94</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3">
@@ -813,7 +1009,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.02</v>
+        <v>34.02</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
@@ -851,13 +1047,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>33.58</v>
+        <v>92.95999999999999</v>
       </c>
       <c r="C6" t="n">
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/Reports/Members/Kelvin_Activity_Report.xlsx
+++ b/Reports/Members/Kelvin_Activity_Report.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sessions" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Summary" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sessions" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:I10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -702,7 +702,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-05-16 17:39:10</t>
+          <t>2026-05-27 09:35:55</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -717,22 +717,171 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>5.34</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr"/>
+          <t>7.56</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="F7" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Garmin</t>
+        </is>
+      </c>
       <c r="H7" t="inlineStr">
         <is>
           <t>View</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-05-29 18:09:22</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kelvin</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Run/Jog</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>7.56</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Garmin Forerunner 265</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-05-30 10:55:11</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kelvin</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Run/Jog</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>8.16</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Southwest</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-06-01 11:41:23</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kelvin</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Run/Jog</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>10.44</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Strava</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
@@ -781,7 +930,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>30.56</v>
+        <v>58.94</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
@@ -851,7 +1000,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>33.58</v>
+        <v>61.96</v>
       </c>
       <c r="C6" t="n">
         <v>0</v>

--- a/Reports/Members/Kelvin_Activity_Report.xlsx
+++ b/Reports/Members/Kelvin_Activity_Report.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I10"/>
+  <dimension ref="A1:I11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -882,6 +882,53 @@
         </is>
       </c>
       <c r="I10" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>6/3/2026 18:59:20</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kelvin</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Run/Jog</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>10.06</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Strava</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
@@ -930,13 +977,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>58.94</v>
+        <v>69</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3">
@@ -1000,13 +1047,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>61.96</v>
+        <v>72.02</v>
       </c>
       <c r="C6" t="n">
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/Reports/Members/Kelvin_Activity_Report.xlsx
+++ b/Reports/Members/Kelvin_Activity_Report.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sessions" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Sessions" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -467,7 +467,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-18 18:45:40</t>
+          <t>2026-05-25 18:37:29</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -482,7 +482,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>7.32</t>
+          <t>7.57</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -514,7 +514,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-20 19:07:24</t>
+          <t>2026-05-27 09:35:55</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -529,7 +529,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>5.31</t>
+          <t>7.56</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -561,7 +561,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-20 19:19:30</t>
+          <t>2026-05-29 18:09:22</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -571,12 +571,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Steps</t>
+          <t>Run/Jog</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>7.56</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -591,7 +591,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Garmin</t>
+          <t>Garmin Forerunner 265</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -608,7 +608,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-23 14:39:30</t>
+          <t>2026-05-30 10:55:11</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -623,7 +623,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>5.02</t>
+          <t>8.16</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Garmin</t>
+          <t>Southwest</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -655,7 +655,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-05-25 18:37:29</t>
+          <t>2026-05-18 18:45:40</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -670,7 +670,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>7.57</t>
+          <t>7.32</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -702,7 +702,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-05-27 09:35:55</t>
+          <t>2026-05-20 19:07:24</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -717,7 +717,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>7.56</t>
+          <t>5.31</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -749,7 +749,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-05-29 18:09:22</t>
+          <t>2026-05-20 19:19:30</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -759,12 +759,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Run/Jog</t>
+          <t>Steps</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>7.56</t>
+          <t>3.02</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -779,7 +779,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Garmin Forerunner 265</t>
+          <t>Garmin</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -796,7 +796,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-05-30 10:55:11</t>
+          <t>2026-05-23 14:39:30</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -811,7 +811,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>8.16</t>
+          <t>5.02</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -826,7 +826,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Southwest</t>
+          <t>Garmin</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">

--- a/Reports/Members/Kelvin_Activity_Report.xlsx
+++ b/Reports/Members/Kelvin_Activity_Report.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sessions" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Summary" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sessions" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -467,7 +467,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-25 18:37:29</t>
+          <t>2026-05-18 18:45:40</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -482,7 +482,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>7.57</t>
+          <t>7.32</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -514,7 +514,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-27 09:35:55</t>
+          <t>2026-05-20 19:07:24</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -529,7 +529,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>7.56</t>
+          <t>5.31</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -561,7 +561,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-29 18:09:22</t>
+          <t>2026-05-20 19:19:30</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -571,12 +571,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Run/Jog</t>
+          <t>Steps</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>7.56</t>
+          <t>3.02</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -591,7 +591,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Garmin Forerunner 265</t>
+          <t>Garmin</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -608,7 +608,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-30 10:55:11</t>
+          <t>2026-05-23 14:39:30</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -623,7 +623,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.16</t>
+          <t>5.02</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Southwest</t>
+          <t>Garmin</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -655,7 +655,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-05-18 18:45:40</t>
+          <t>2026-05-25 18:37:29</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -670,7 +670,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>7.32</t>
+          <t>7.57</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -702,7 +702,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-05-20 19:07:24</t>
+          <t>2026-05-27 09:35:55</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -717,7 +717,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>5.31</t>
+          <t>7.56</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -749,7 +749,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-05-20 19:19:30</t>
+          <t>2026-05-29 18:09:22</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -759,12 +759,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Steps</t>
+          <t>Run/Jog</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>7.56</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -779,7 +779,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Garmin</t>
+          <t>Garmin Forerunner 265</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -796,7 +796,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-05-23 14:39:30</t>
+          <t>2026-05-30 10:55:11</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -811,7 +811,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>5.02</t>
+          <t>8.16</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -826,7 +826,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Garmin</t>
+          <t>Southwest</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">

--- a/Reports/Members/Kelvin_Activity_Report.xlsx
+++ b/Reports/Members/Kelvin_Activity_Report.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sessions" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Sessions" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I11"/>
+  <dimension ref="A1:I12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -467,7 +467,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-18 18:45:40</t>
+          <t>2026-05-25 18:37:29</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -482,7 +482,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>7.32</t>
+          <t>7.57</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -514,7 +514,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-20 19:07:24</t>
+          <t>2026-05-27 09:35:55</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -529,7 +529,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>5.31</t>
+          <t>7.56</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -561,7 +561,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-20 19:19:30</t>
+          <t>2026-05-29 18:09:22</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -571,12 +571,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Steps</t>
+          <t>Run/Jog</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>7.56</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -591,7 +591,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Garmin</t>
+          <t>Garmin Forerunner 265</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -608,7 +608,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-23 14:39:30</t>
+          <t>2026-05-30 10:55:11</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -623,7 +623,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>5.02</t>
+          <t>8.16</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Garmin</t>
+          <t>Southwest</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -655,7 +655,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-05-25 18:37:29</t>
+          <t>2026-05-18 18:45:40</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -670,7 +670,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>7.57</t>
+          <t>7.32</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -702,7 +702,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-05-27 09:35:55</t>
+          <t>2026-05-20 19:07:24</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -717,7 +717,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>7.56</t>
+          <t>5.31</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -749,7 +749,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-05-29 18:09:22</t>
+          <t>2026-05-20 19:19:30</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -759,12 +759,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Run/Jog</t>
+          <t>Steps</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>7.56</t>
+          <t>3.02</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -779,7 +779,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Garmin Forerunner 265</t>
+          <t>Garmin</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -796,7 +796,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-05-30 10:55:11</t>
+          <t>2026-05-23 14:39:30</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -811,7 +811,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>8.16</t>
+          <t>5.02</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -826,7 +826,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Southwest</t>
+          <t>Garmin</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -931,6 +931,53 @@
       <c r="I11" t="inlineStr">
         <is>
           <t>Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>6/6/2026 8:36:45</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kelvin</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Run/Jog</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>10.25</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Committee Approval Required</t>
         </is>
       </c>
     </row>
@@ -977,13 +1024,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>69</v>
+        <v>79.25</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3">
@@ -1047,13 +1094,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>72.02</v>
+        <v>82.27</v>
       </c>
       <c r="C6" t="n">
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>

--- a/Reports/Members/Kelvin_Activity_Report.xlsx
+++ b/Reports/Members/Kelvin_Activity_Report.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I12"/>
+  <dimension ref="A1:I13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -976,6 +976,53 @@
         </is>
       </c>
       <c r="I12" t="inlineStr">
+        <is>
+          <t>Committee Approval Required</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>6/7/2026 12:17:03</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Kelvin</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Run/Jog</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>10.35</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
         <is>
           <t>Committee Approval Required</t>
         </is>
@@ -1024,13 +1071,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>79.25</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3">
@@ -1094,13 +1141,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>82.27</v>
+        <v>92.62</v>
       </c>
       <c r="C6" t="n">
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>

--- a/Reports/Members/Kelvin_Activity_Report.xlsx
+++ b/Reports/Members/Kelvin_Activity_Report.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sessions" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Summary" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sessions" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -467,7 +467,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-25 18:37:29</t>
+          <t>2026-05-18 18:45:40</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -482,7 +482,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>7.57</t>
+          <t>7.32</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -514,7 +514,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-27 09:35:55</t>
+          <t>2026-05-20 19:07:24</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -529,7 +529,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>7.56</t>
+          <t>5.31</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -561,7 +561,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-29 18:09:22</t>
+          <t>2026-05-20 19:19:30</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -571,12 +571,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Run/Jog</t>
+          <t>Steps</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>7.56</t>
+          <t>3.02</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -591,7 +591,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Garmin Forerunner 265</t>
+          <t>Garmin</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -608,7 +608,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-30 10:55:11</t>
+          <t>2026-05-23 14:39:30</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -623,7 +623,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.16</t>
+          <t>5.02</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Southwest</t>
+          <t>Garmin</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -655,7 +655,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-05-18 18:45:40</t>
+          <t>2026-05-25 18:37:29</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -670,7 +670,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>7.32</t>
+          <t>7.57</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -702,7 +702,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-05-20 19:07:24</t>
+          <t>2026-05-27 09:35:55</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -717,7 +717,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>5.31</t>
+          <t>7.56</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -749,7 +749,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-05-20 19:19:30</t>
+          <t>2026-05-29 18:09:22</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -759,12 +759,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Steps</t>
+          <t>Run/Jog</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>7.56</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -779,7 +779,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Garmin</t>
+          <t>Garmin Forerunner 265</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -796,7 +796,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-05-23 14:39:30</t>
+          <t>2026-05-30 10:55:11</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -811,7 +811,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>5.02</t>
+          <t>8.16</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -826,7 +826,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Garmin</t>
+          <t>Southwest</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -967,7 +967,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Strava</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Committee Approval Required</t>
+          <t>Verified</t>
         </is>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Strava</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1024,7 +1024,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Committee Approval Required</t>
+          <t>Verified</t>
         </is>
       </c>
     </row>

--- a/Reports/Members/Kelvin_Activity_Report.xlsx
+++ b/Reports/Members/Kelvin_Activity_Report.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I13"/>
+  <dimension ref="A1:I14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1025,6 +1025,53 @@
       <c r="I13" t="inlineStr">
         <is>
           <t>Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>6/9/2026 9:34:20</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Kelvin</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Run/Jog</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>10.30</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Garmin</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Flagged</t>
         </is>
       </c>
     </row>
@@ -1071,13 +1118,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>89.59999999999999</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3">
@@ -1141,13 +1188,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>92.62</v>
+        <v>102.92</v>
       </c>
       <c r="C6" t="n">
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>

--- a/Reports/Members/Kelvin_Activity_Report.xlsx
+++ b/Reports/Members/Kelvin_Activity_Report.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I14"/>
+  <dimension ref="A1:I15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1031,45 +1031,92 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>6/10/2026 19:24:21</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Kelvin</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Run/Jog</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>10.36</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Committee Approval Required</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
           <t>6/9/2026 9:34:20</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Kelvin</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Run/Jog</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Kelvin</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Run/Jog</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
         <is>
           <t>10.30</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>Garmin</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
         <is>
           <t>Flagged</t>
         </is>
@@ -1118,13 +1165,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>99.90000000000001</v>
+        <v>110.26</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3">
@@ -1188,13 +1235,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>102.92</v>
+        <v>113.28</v>
       </c>
       <c r="C6" t="n">
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>

--- a/Reports/Members/Kelvin_Activity_Report.xlsx
+++ b/Reports/Members/Kelvin_Activity_Report.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sessions" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Sessions" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I15"/>
+  <dimension ref="A1:I17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -467,7 +467,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-18 18:45:40</t>
+          <t>2026-05-25 18:37:29</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -482,7 +482,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>7.32</t>
+          <t>7.57</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -514,7 +514,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-20 19:07:24</t>
+          <t>2026-05-27 09:35:55</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -529,7 +529,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>5.31</t>
+          <t>7.56</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -561,7 +561,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-20 19:19:30</t>
+          <t>2026-05-29 18:09:22</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -571,12 +571,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Steps</t>
+          <t>Run/Jog</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>7.56</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -591,7 +591,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Garmin</t>
+          <t>Garmin Forerunner 265</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -608,7 +608,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-23 14:39:30</t>
+          <t>2026-05-30 10:55:11</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -623,7 +623,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>5.02</t>
+          <t>8.16</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Garmin</t>
+          <t>Southwest</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -655,7 +655,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-05-25 18:37:29</t>
+          <t>2026-05-18 18:45:40</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -670,7 +670,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>7.57</t>
+          <t>7.32</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -702,7 +702,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-05-27 09:35:55</t>
+          <t>2026-05-20 19:07:24</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -717,7 +717,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>7.56</t>
+          <t>5.31</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -749,7 +749,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-05-29 18:09:22</t>
+          <t>2026-05-20 19:19:30</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -759,12 +759,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Run/Jog</t>
+          <t>Steps</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>7.56</t>
+          <t>3.02</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -779,7 +779,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Garmin Forerunner 265</t>
+          <t>Garmin</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -796,7 +796,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-05-30 10:55:11</t>
+          <t>2026-05-23 14:39:30</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -811,7 +811,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>8.16</t>
+          <t>5.02</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -826,7 +826,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Southwest</t>
+          <t>Garmin</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1078,45 +1078,139 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>6/11/2026 19:31:48</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Kelvin</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Run/Jog</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>10.28</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Garmin</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Flagged</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>6/12/2026 9:52:56</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Kelvin</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Run/Jog</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>10.22</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Committee Approval Required</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
           <t>6/9/2026 9:34:20</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Kelvin</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Run/Jog</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Kelvin</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Run/Jog</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
         <is>
           <t>10.30</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t>Garmin</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
         <is>
           <t>Flagged</t>
         </is>
@@ -1165,13 +1259,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>110.26</v>
+        <v>130.76</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3">
@@ -1235,13 +1329,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>113.28</v>
+        <v>133.78</v>
       </c>
       <c r="C6" t="n">
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
     </row>
   </sheetData>
